--- a/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ugo est au pré avec maman. Un cheval mange. Une jument est là. Un poulain reste près. Maman dit : trois noms de la famille. Ugo répète : cheval, jument, poulain. Près du foin : un chien, une chienne, un chiot. Ugo dit les trois noms. Encore : coq, poule, poussin. Ugo pose le doigt vers le poussin. Maman dit : le petit, c'est le poussin.</t>
+          <t>Ugo est au pré avec maman. Un cheval mange. Une jument est là. Un poulain reste près. Trois noms de la famille. Ugo répète : cheval, jument, poulain. Près du foin : un chien, une chienne, un chiot. Ugo dit les trois noms. Encore : coq, poule, poussin. Ugo pose le doigt vers le poussin. Le petit, c'est le poussin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ugo est au pré avec maman. Un cheval mange. Une jument est là. Un poulain reste près.
+maman|Trois noms de la famille.
+narrateur|Ugo répète : cheval, jument, poulain. Près du foin : un chien, une chienne, un chiot. Ugo dit les trois noms. Encore : coq, poule, poussin. Ugo pose le doigt vers le poussin.
+maman|Le petit, c'est le poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ugo a dit les trois noms. Cheval, jument, poulain. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le seau. Ugo salue le poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 maman|Le petit, c'est le poussin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1506,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1678,7 @@
           <t>narrateur|Ugo a dit les trois noms. Cheval, jument, poulain. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1842,7 @@
           <t>narrateur|Maman range le seau. Ugo salue le poulain.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ugo dit les trois noms du pré</t>
+          <t>La carotte de l'âne</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut donner une carotte à l'âne. La carotte glisse dans l'herbe. Elle la retrouve. Âne, ânesse et ânon s'approchent. L'âne croque.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ugo est au pré avec maman. Un cheval mange. Une jument est là. Un poulain reste près. Trois noms de la famille. Ugo répète : cheval, jument, poulain. Près du foin : un chien, une chienne, un chiot. Ugo dit les trois noms. Encore : coq, poule, poussin. Ugo pose le doigt vers le poussin. Le petit, c'est le poussin.</t>
+          <t>L'herbe du pré sent le foin chaud. Des sauterelles sautent devant les bottes. Le ciel est pâle, presque blanc. Chouchou vit ici, avec maman. Dans sa poche, une carotte fait un rond. Maman, je veux la donner à l'âne. La carotte ? Oui. Il aime le croquant. En ce moment, elles marchent le long du fil. Le fil est chaud, un peu rouillé. Une ânesse grise broute près du chardon. L'ânesse ! Oui, Chouchou. Elle a de grandes oreilles. Un ânon reste collé à son flanc. L'ânon aussi. Tu le vois bien ? Oui. L'âne est où ? Plus loin, près du saule. Chouchou sort la carotte. Elle est fraîche, encore un peu terreuse. Un pas trop vite : la carotte glisse. Elle disparaît dans l'herbe haute. Oh. Elle est tombée. On la cherche ensemble ? Chouchou écarte les brins, tout doux. Une pointe orange brille entre deux tiges. Je l'ai ! Merci d'avoir cherché sans courir. L'âne gris s'approche du fil. L'âne ! Âne, ânesse, ânon. Trois noms de la famille. Chouchou tend la carotte sur sa paume. L'âne la prend avec des lèvres de velours. Ça chatouille. Tu lui as donné tout calme. L'âne mâche, la mâchoire de travers. Un bout de carotte tombe, puis remonte. Il a des poils aux oreilles. Oui. De grandes oreilles chaudes. L'ânesse avance d'un pas, puis s'arrête. L'ânon reste collé, l'œil sombre. Il a un peu peur. On reste de ce côté du fil. Chouchou essuie un peu de terre au pantalon. Ta poche est vide, maintenant. La carotte est dans l'âne.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ugo est au pré avec maman. Un cheval mange. Une jument est là. Un poulain reste près. Maman dit : &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms de la famille. Ugo répète : cheval, jument, poulain. Près du foin : un chien, une chienne, un chiot. Ugo dit les trois noms. Encore : coq, poule, poussin. Ugo pose le doigt vers le poussin. Maman dit : le petit, c'est le poussin.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'herbe du pré sent le foin chaud. Des sauterelles sautent devant les bottes. Le ciel est pâle, presque blanc. Chouchou vit ici, avec maman. Dans sa poche, une carotte fait un rond. Maman, je veux la donner à l'âne. La carotte ? Oui. Il aime le croquant. En ce moment, elles marchent le long du fil. Le fil est chaud, un peu rouillé. Une ânesse grise broute près du chardon. L'ânesse ! Oui, Chouchou. Elle a de grandes oreilles. Un ânon reste collé à son flanc. L'ânon aussi. Tu le vois bien ? Oui. L'âne est où ? Plus loin, près du saule. Chouchou sort la carotte. Elle est fraîche, encore un peu terreuse. Un pas trop vite : la carotte glisse. Elle disparaît dans l'herbe haute. Oh. Elle est tombée. On la cherche ensemble ? Chouchou écarte les brins, tout doux. Une pointe orange brille entre deux tiges. Je l'ai ! Merci d'avoir cherché sans courir. L'âne gris s'approche du fil. L'âne ! Âne, ânesse, ânon. Trois noms de la famille. Chouchou tend la carotte sur sa paume. L'âne la prend avec des lèvres de velours. Ça chatouille. Tu lui as donné tout calme. L'âne mâche, la mâchoire de travers. Un bout de carotte tombe, puis remonte. Il a des poils aux oreilles. Oui. De grandes oreilles chaudes. L'ânesse avance d'un pas, puis s'arrête. L'ânon reste collé, l'œil sombre. Il a un peu peur. On reste de ce côté du fil. Chouchou essuie un peu de terre au pantalon. Ta poche est vide, maintenant. La carotte est dans l'âne.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,10 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ugo est au pré avec maman. Un cheval mange. Une jument est là. Un poulain reste près.
+          <t>narrateur|L'herbe du pré sent le foin chaud.
+narrateur|Des sauterelles sautent devant les bottes.
+narrateur|Le ciel est pâle, presque blanc.
+narrateur|Chouchou vit ici, avec maman.
+narrateur|Dans sa poche, une carotte fait un rond.
+enfant-f|Maman, je veux la donner à l'âne.
+maman|La carotte ?
+enfant-f|Oui.
+enfant-f|Il aime le croquant.
+narrateur|En ce moment, elles marchent le long du fil.
+narrateur|Le fil est chaud, un peu rouillé.
+narrateur|Une ânesse grise broute près du chardon.
+enfant-f|L'ânesse !
+maman|Oui, Chouchou.
+maman|Elle a de grandes oreilles.
+narrateur|Un ânon reste collé à son flanc.
+enfant-f|L'ânon aussi.
+maman|Tu le vois bien ?
+enfant-f|Oui.
+enfant-f|L'âne est où ?
+maman|Plus loin, près du saule.
+narrateur|Chouchou sort la carotte.
+narrateur|Elle est fraîche, encore un peu terreuse.
+narrateur|Un pas trop vite : la carotte glisse.
+narrateur|Elle disparaît dans l'herbe haute.
+enfant-f|Oh.
+enfant-f|Elle est tombée.
+maman|On la cherche ensemble ?
+narrateur|Chouchou écarte les brins, tout doux.
+narrateur|Une pointe orange brille entre deux tiges.
+enfant-f|Je l'ai !
+maman|Merci d'avoir cherché sans courir.
+narrateur|L'âne gris s'approche du fil.
+enfant-f|L'âne !
+maman|Âne, ânesse, ânon.
 maman|Trois noms de la famille.
-narrateur|Ugo répète : cheval, jument, poulain. Près du foin : un chien, une chienne, un chiot. Ugo dit les trois noms. Encore : coq, poule, poussin. Ugo pose le doigt vers le poussin.
-maman|Le petit, c'est le poussin.</t>
+narrateur|Chouchou tend la carotte sur sa paume.
+narrateur|L'âne la prend avec des lèvres de velours.
+enfant-f|Ça chatouille.
+maman|Tu lui as donné tout calme.
+narrateur|L'âne mâche, la mâchoire de travers.
+narrateur|Un bout de carotte tombe, puis remonte.
+enfant-f|Il a des poils aux oreilles.
+maman|Oui.
+maman|De grandes oreilles chaudes.
+narrateur|L'ânesse avance d'un pas, puis s'arrête.
+narrateur|L'ânon reste collé, l'œil sombre.
+enfant-f|Il a un peu peur.
+maman|On reste de ce côté du fil.
+narrateur|Chouchou essuie un peu de terre au pantalon.
+maman|Ta poche est vide, maintenant.
+enfant-f|La carotte est dans l'âne.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1347,12 +1407,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le coq, la poule, et le petit. Quel est le petit ?</t>
+          <t>Chouchou tend la carotte à qui ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le coq, la poule, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou tend la carotte à qui ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,12 +1422,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>poussin</t>
+          <t>âne</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>poussin | le poussin | poulain | le petit</t>
+          <t>âne | l'âne | a l'âne | à l'âne</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1442,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Les trois noms de la famille. Le petit, c'est qui ?</t>
+          <t>C'est l'âne. À qui tend-elle la carotte ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1431,7 +1491,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,10 +1563,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou tend la carotte à qui ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ugo a dit les trois noms. Cheval, jument, poulain. Coq, poule, poussin.</t>
+          <t>L'âne croque, lentement. Un peu de jus orange perle au poil. Il aime ça. Oui. C'est l'âne du pré. L'ânesse regarde, elle aussi. L'ânon se cache un peu. Chouchou essuie sa paume dans l'herbe. On reste encore ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ugo a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Cheval, jument, poulain. Coq, poule, poussin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'âne croque, lentement. Un peu de jus orange perle au poil. Il aime ça. Oui. C'est l'âne du pré. L'ânesse regarde, elle aussi. L'ânon se cache un peu. Chouchou essuie sa paume dans l'herbe. On reste encore ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1599,7 +1658,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1675,10 +1734,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ugo a dit les trois noms. Cheval, jument, poulain. Coq, poule, poussin.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|L'âne croque, lentement.
+narrateur|Un peu de jus orange perle au poil.
+enfant-f|Il aime ça.
+maman|Oui.
+maman|C'est l'âne du pré.
+maman|L'ânesse regarde, elle aussi.
+enfant-f|L'ânon se cache un peu.
+narrateur|Chouchou essuie sa paume dans l'herbe.
+maman|On reste encore ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,12 +1770,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Ugo salue le poulain.</t>
+          <t>Elles reculent vers le chemin de terre. L'ânesse reprend le chardon. L'ânon colle à nouveau son flanc. L'âne mâche encore. Ta carotte. Tu as vu les trois ? Âne, ânesse, ânon. Chouchou sent encore le sucré sur les doigts. Et un peu de terre. De la carotte. Une sauterelle reprend le chemin des bottes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le seau. Ugo salue le poulain.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles reculent vers le chemin de terre. L'ânesse reprend le chardon. L'ânon colle à nouveau son flanc. L'âne mâche encore. Ta carotte. Tu as vu les trois ? Âne, ânesse, ânon. Chouchou sent encore le sucré sur les doigts. Et un peu de terre. De la carotte. Une sauterelle reprend le chemin des bottes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1771,7 +1838,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,10 +1906,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau. Ugo salue le poulain.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles reculent vers le chemin de terre.
+narrateur|L'ânesse reprend le chardon.
+narrateur|L'ânon colle à nouveau son flanc.
+enfant-f|L'âne mâche encore.
+maman|Ta carotte.
+maman|Tu as vu les trois ?
+enfant-f|Âne, ânesse, ânon.
+narrateur|Chouchou sent encore le sucré sur les doigts.
+maman|Et un peu de terre.
+enfant-f|De la carotte.
+narrateur|Une sauterelle reprend le chemin des bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Il croque, maman. Tout doux. L'âne croque la carotte, lentement.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il croque, maman. Tout doux. L'âne croque la carotte, lentement.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1928,14 +2004,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,10 +2083,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Il croque, maman.
+maman|Tout doux.
+narrateur|L'âne croque la carotte, lentement.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>pré d'été, clôture, carotte</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ugo, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
